--- a/test_data/functional_parity_scenarios.xlsx
+++ b/test_data/functional_parity_scenarios.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rishabhbhangale/Downloads/semantics/Lenovo Qlik/test_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4345E8BE-CAE2-7E41-BF9D-84F189CFA6F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4D8754A-D152-0349-A72A-C453922BC9FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17340" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="74">
   <si>
     <t>Test ID</t>
   </si>
@@ -148,9 +148,6 @@
     <t>ALL</t>
   </si>
   <si>
-    <t>N/A</t>
-  </si>
-  <si>
     <t>In-Scope Sheets</t>
   </si>
   <si>
@@ -166,15 +163,6 @@
     <t>In-Scope Pages</t>
   </si>
   <si>
-    <t>Overdue Opportunities ISG</t>
-  </si>
-  <si>
-    <t>7 Days Opportunities ISG</t>
-  </si>
-  <si>
-    <t>Missing PN Opportunities ISG</t>
-  </si>
-  <si>
     <t>Sheet Catalog</t>
   </si>
   <si>
@@ -187,10 +175,7 @@
     <t>Visuals</t>
   </si>
   <si>
-    <t>Date; GEO Level 3</t>
-  </si>
-  <si>
-    <t>Calendar[Date]; GEO Level 3</t>
+    <t>GEO Level3</t>
   </si>
   <si>
     <t>Measure Toggle</t>
@@ -208,13 +193,13 @@
     <t>Exists</t>
   </si>
   <si>
-    <t>2026-08; BENELUX, CH</t>
-  </si>
-  <si>
-    <t>2026-09; CZ/SK, EECA</t>
-  </si>
-  <si>
-    <t>2026-09; FRANCE, GAT</t>
+    <t>BENELUX, CH</t>
+  </si>
+  <si>
+    <t>CZ/SK, EECA</t>
+  </si>
+  <si>
+    <t>FRANCE, GAT</t>
   </si>
   <si>
     <t>Toggle</t>
@@ -630,10 +615,9 @@
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="35" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="23.5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="22.1640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="20.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.33203125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="56.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -676,17 +660,14 @@
       <c r="D2" t="s">
         <v>41</v>
       </c>
-      <c r="E2" t="s">
-        <v>42</v>
-      </c>
       <c r="F2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G2" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="H2" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
@@ -699,20 +680,17 @@
       <c r="C3" t="s">
         <v>29</v>
       </c>
-      <c r="D3" t="s">
-        <v>42</v>
-      </c>
       <c r="E3" t="s">
         <v>41</v>
       </c>
       <c r="F3" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G3" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="H3" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
@@ -726,19 +704,19 @@
         <v>30</v>
       </c>
       <c r="D4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F4" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G4" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="H4" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
@@ -752,19 +730,19 @@
         <v>31</v>
       </c>
       <c r="D5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E5" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="F5" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="G5" t="s">
         <v>41</v>
       </c>
       <c r="H5" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
@@ -778,19 +756,19 @@
         <v>32</v>
       </c>
       <c r="D6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E6" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="F6" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="G6" t="s">
         <v>41</v>
       </c>
       <c r="H6" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
@@ -804,19 +782,19 @@
         <v>33</v>
       </c>
       <c r="D7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E7" t="s">
+        <v>45</v>
+      </c>
+      <c r="F7" t="s">
         <v>50</v>
-      </c>
-      <c r="F7" t="s">
-        <v>54</v>
       </c>
       <c r="G7" t="s">
         <v>41</v>
       </c>
       <c r="H7" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
@@ -830,19 +808,19 @@
         <v>34</v>
       </c>
       <c r="D8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E8" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="F8" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="G8" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="H8" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
@@ -856,19 +834,19 @@
         <v>35</v>
       </c>
       <c r="D9" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E9" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="F9" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="G9" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="H9" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
@@ -882,19 +860,19 @@
         <v>36</v>
       </c>
       <c r="D10" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E10" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="F10" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="G10" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="H10" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
@@ -908,19 +886,19 @@
         <v>37</v>
       </c>
       <c r="D11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E11" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="F11" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="G11" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="H11" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
@@ -934,19 +912,19 @@
         <v>38</v>
       </c>
       <c r="D12" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E12" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="F12" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="G12" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="H12" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
@@ -960,19 +938,19 @@
         <v>39</v>
       </c>
       <c r="D13" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E13" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="F13" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="G13" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="H13" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
@@ -986,19 +964,19 @@
         <v>40</v>
       </c>
       <c r="D14" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E14" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="F14" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="G14" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="H14" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
     </row>
   </sheetData>

--- a/test_data/functional_parity_scenarios.xlsx
+++ b/test_data/functional_parity_scenarios.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rishabhbhangale/Downloads/semantics/Lenovo Qlik/test_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4D8754A-D152-0349-A72A-C453922BC9FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F134C834-C554-174C-8230-01FAACE8C68B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="44">
   <si>
     <t>Test ID</t>
   </si>
@@ -64,48 +64,18 @@
     <t>FP-B-003</t>
   </si>
   <si>
-    <t>FP-C-001</t>
-  </si>
-  <si>
-    <t>FP-D-001</t>
-  </si>
-  <si>
-    <t>FP-D-002</t>
-  </si>
-  <si>
-    <t>FP-D-003</t>
-  </si>
-  <si>
-    <t>FP-E-001</t>
-  </si>
-  <si>
     <t>FP-F-001</t>
   </si>
   <si>
-    <t>FP-G-001</t>
-  </si>
-  <si>
     <t>A</t>
   </si>
   <si>
     <t>B</t>
   </si>
   <si>
-    <t>C</t>
-  </si>
-  <si>
-    <t>D</t>
-  </si>
-  <si>
-    <t>E</t>
-  </si>
-  <si>
     <t>F</t>
   </si>
   <si>
-    <t>G</t>
-  </si>
-  <si>
     <t>Dynamic Qlik Sheet Discovery</t>
   </si>
   <si>
@@ -124,27 +94,9 @@
     <t>Visual Existence: Missing PN Opportunities</t>
   </si>
   <si>
-    <t>Slicer Existence: Date and GEO Level 3</t>
-  </si>
-  <si>
-    <t>Core Parity: Rev of Overdue Opportunities</t>
-  </si>
-  <si>
-    <t>Core Parity: Rev of 7 Days Opportunities</t>
-  </si>
-  <si>
-    <t>Core Parity: Rev of Missing PN Opportunities</t>
-  </si>
-  <si>
-    <t>Measure Toggle: Revenue vs Quantity</t>
-  </si>
-  <si>
     <t>Cross-Filter Segment Click: FRANCE</t>
   </si>
   <si>
-    <t>Filter Clear &amp; State Isolation</t>
-  </si>
-  <si>
     <t>ALL</t>
   </si>
   <si>
@@ -175,42 +127,18 @@
     <t>Visuals</t>
   </si>
   <si>
-    <t>GEO Level3</t>
-  </si>
-  <si>
-    <t>Measure Toggle</t>
-  </si>
-  <si>
     <t>Market</t>
   </si>
   <si>
-    <t>Toolbar Clear All</t>
-  </si>
-  <si>
     <t>Enumerate</t>
   </si>
   <si>
     <t>Exists</t>
   </si>
   <si>
-    <t>BENELUX, CH</t>
-  </si>
-  <si>
-    <t>CZ/SK, EECA</t>
-  </si>
-  <si>
-    <t>FRANCE, GAT</t>
-  </si>
-  <si>
-    <t>Toggle</t>
-  </si>
-  <si>
     <t>FRANCE</t>
   </si>
   <si>
-    <t>Clear All</t>
-  </si>
-  <si>
     <t>Discover all published Qlik sheets dynamically</t>
   </si>
   <si>
@@ -223,25 +151,7 @@
     <t>Verify visual charts and tables are rendered</t>
   </si>
   <si>
-    <t>Verify required slicers are rendered on PBI page</t>
-  </si>
-  <si>
-    <t>Filter Date to 2026-08, GEO Level 3 to BENELUX, CH; verify visual parity</t>
-  </si>
-  <si>
-    <t>Filter Date to 2026-09, GEO Level 3 to CZ/SK, EECA; verify visual parity</t>
-  </si>
-  <si>
-    <t>Filter Date to 2026-09, GEO Level 3 to FRANCE, GAT; verify visual parity</t>
-  </si>
-  <si>
-    <t>Switch between Revenue and Quantity measures and verify visual update</t>
-  </si>
-  <si>
     <t>Clicking market segment propagates filter to cards</t>
-  </si>
-  <si>
-    <t>Clearing slicers restores initial baseline state with zero filter bleed</t>
   </si>
 </sst>
 </file>
@@ -609,7 +519,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
@@ -652,22 +562,22 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="D2" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="F2" t="s">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="G2" t="s">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="H2" t="s">
-        <v>63</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
@@ -675,22 +585,22 @@
         <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="E3" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="F3" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="G3" t="s">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="H3" t="s">
-        <v>64</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
@@ -698,25 +608,25 @@
         <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4" t="s">
         <v>30</v>
       </c>
-      <c r="D4" t="s">
-        <v>42</v>
-      </c>
-      <c r="E4" t="s">
-        <v>46</v>
-      </c>
       <c r="F4" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="G4" t="s">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="H4" t="s">
-        <v>65</v>
+        <v>41</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
@@ -724,25 +634,25 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="C5" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="D5" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="E5" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="F5" t="s">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="G5" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="H5" t="s">
-        <v>66</v>
+        <v>42</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
@@ -750,25 +660,25 @@
         <v>12</v>
       </c>
       <c r="B6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" t="s">
         <v>22</v>
       </c>
-      <c r="C6" t="s">
-        <v>32</v>
-      </c>
       <c r="D6" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="E6" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="F6" t="s">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="G6" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="H6" t="s">
-        <v>66</v>
+        <v>42</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
@@ -776,25 +686,25 @@
         <v>13</v>
       </c>
       <c r="B7" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="C7" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="D7" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="E7" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="F7" t="s">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="G7" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="H7" t="s">
-        <v>66</v>
+        <v>42</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
@@ -802,181 +712,25 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C8" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="D8" t="s">
+        <v>29</v>
+      </c>
+      <c r="E8" t="s">
+        <v>29</v>
+      </c>
+      <c r="F8" t="s">
+        <v>35</v>
+      </c>
+      <c r="G8" t="s">
+        <v>38</v>
+      </c>
+      <c r="H8" t="s">
         <v>43</v>
-      </c>
-      <c r="E8" t="s">
-        <v>43</v>
-      </c>
-      <c r="F8" t="s">
-        <v>51</v>
-      </c>
-      <c r="G8" t="s">
-        <v>56</v>
-      </c>
-      <c r="H8" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>15</v>
-      </c>
-      <c r="B9" t="s">
-        <v>24</v>
-      </c>
-      <c r="C9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D9" t="s">
-        <v>43</v>
-      </c>
-      <c r="E9" t="s">
-        <v>43</v>
-      </c>
-      <c r="F9" t="s">
-        <v>51</v>
-      </c>
-      <c r="G9" t="s">
-        <v>57</v>
-      </c>
-      <c r="H9" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>16</v>
-      </c>
-      <c r="B10" t="s">
-        <v>24</v>
-      </c>
-      <c r="C10" t="s">
-        <v>36</v>
-      </c>
-      <c r="D10" t="s">
-        <v>44</v>
-      </c>
-      <c r="E10" t="s">
-        <v>44</v>
-      </c>
-      <c r="F10" t="s">
-        <v>51</v>
-      </c>
-      <c r="G10" t="s">
-        <v>58</v>
-      </c>
-      <c r="H10" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>17</v>
-      </c>
-      <c r="B11" t="s">
-        <v>24</v>
-      </c>
-      <c r="C11" t="s">
-        <v>37</v>
-      </c>
-      <c r="D11" t="s">
-        <v>45</v>
-      </c>
-      <c r="E11" t="s">
-        <v>45</v>
-      </c>
-      <c r="F11" t="s">
-        <v>51</v>
-      </c>
-      <c r="G11" t="s">
-        <v>59</v>
-      </c>
-      <c r="H11" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>18</v>
-      </c>
-      <c r="B12" t="s">
-        <v>25</v>
-      </c>
-      <c r="C12" t="s">
-        <v>38</v>
-      </c>
-      <c r="D12" t="s">
-        <v>43</v>
-      </c>
-      <c r="E12" t="s">
-        <v>43</v>
-      </c>
-      <c r="F12" t="s">
-        <v>52</v>
-      </c>
-      <c r="G12" t="s">
-        <v>60</v>
-      </c>
-      <c r="H12" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>19</v>
-      </c>
-      <c r="B13" t="s">
-        <v>26</v>
-      </c>
-      <c r="C13" t="s">
-        <v>39</v>
-      </c>
-      <c r="D13" t="s">
-        <v>45</v>
-      </c>
-      <c r="E13" t="s">
-        <v>45</v>
-      </c>
-      <c r="F13" t="s">
-        <v>53</v>
-      </c>
-      <c r="G13" t="s">
-        <v>61</v>
-      </c>
-      <c r="H13" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
-        <v>20</v>
-      </c>
-      <c r="B14" t="s">
-        <v>27</v>
-      </c>
-      <c r="C14" t="s">
-        <v>40</v>
-      </c>
-      <c r="D14" t="s">
-        <v>43</v>
-      </c>
-      <c r="E14" t="s">
-        <v>43</v>
-      </c>
-      <c r="F14" t="s">
-        <v>54</v>
-      </c>
-      <c r="G14" t="s">
-        <v>62</v>
-      </c>
-      <c r="H14" t="s">
-        <v>73</v>
       </c>
     </row>
   </sheetData>
